--- a/AAII_Financials/Yearly/TRUMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TRUMY_YR_FIN.xlsx
@@ -302,7 +302,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -344,7 +344,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>

--- a/AAII_Financials/Yearly/TRUMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TRUMY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="92">
   <si>
     <t>TRUMY</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t xml:space="preserve">Change In Cash and Cash Equivalents </t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -653,135 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44286</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43921</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43555</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6919400</v>
+      </c>
+      <c r="E8" s="3">
         <v>6094800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6170000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5791600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5550200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5844700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5410000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5534300</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3175300</v>
+      </c>
+      <c r="E9" s="3">
         <v>2914500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3030400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2750200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2596900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2648300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2463500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2527600</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3744100</v>
+      </c>
+      <c r="E10" s="3">
         <v>3180300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3139700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3041500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2953200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3196300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2946500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3006800</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -793,35 +808,39 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="3">
         <v>552800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>568200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>426900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>443900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>470400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>430300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>389300</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -846,63 +865,72 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>124600</v>
+      </c>
+      <c r="E14" s="3">
         <v>3900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>46800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>17100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>10800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>16700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>13200</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>570600</v>
+      </c>
+      <c r="E15" s="3">
         <v>377700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>395900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>166900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>172700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>175500</v>
-      </c>
-      <c r="I15" s="3">
-        <v>129000</v>
       </c>
       <c r="J15" s="3">
         <v>129000</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K15" s="3">
+        <v>129000</v>
+      </c>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -911,62 +939,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>5741900</v>
+      </c>
+      <c r="E17" s="3">
         <v>5165500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5238300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4830900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4669100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4823800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4476800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4517000</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1177500</v>
+      </c>
+      <c r="E18" s="3">
         <v>929300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>931700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>960700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>881000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1020900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>933200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1017300</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -978,143 +1013,159 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>6700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-7500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-22400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>7200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-8800</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1745000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1309700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1320900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1135100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1076100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1189200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1063000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1155200</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E22" s="3">
         <v>13700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>16800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>13500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>20000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>17000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>18500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>17000</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1032200</v>
+      </c>
+      <c r="E23" s="3">
         <v>931100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>873600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>942900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>877600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>989400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>926900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1004000</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>251100</v>
+      </c>
+      <c r="E24" s="3">
         <v>227800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>201700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>211500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>179600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>199100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>211400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>145300</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1139,63 +1190,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>781200</v>
+      </c>
+      <c r="E26" s="3">
         <v>703300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>671900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>731400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>698000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>790300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>715500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>858700</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>781200</v>
+      </c>
+      <c r="E27" s="3">
         <v>703300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>672000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>731400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>698600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>791900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>717200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>859600</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1220,9 +1280,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1247,9 +1310,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1274,9 +1340,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1301,63 +1370,72 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E32" s="3">
         <v>2700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-6700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>7500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>22400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-7200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>8800</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>781200</v>
+      </c>
+      <c r="E33" s="3">
         <v>703300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>671900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>731400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>698600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>791900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>717200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>859600</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1382,68 +1460,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>781200</v>
+      </c>
+      <c r="E35" s="3">
         <v>703300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>671900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>731400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>698600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>791900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>717200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>859600</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44286</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43921</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43555</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1455,8 +1542,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1468,47 +1556,51 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>1481600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1354600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1409100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1690200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1815300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1551100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1109800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1580300</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>9700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>500</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -1521,198 +1613,222 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1202500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1190400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1155100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1126300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1168900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1240400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1159300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1148100</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1965900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1894800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1877800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1634900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1587500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1367500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1210200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1055200</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>181400</v>
+      </c>
+      <c r="E45" s="3">
         <v>238900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>71800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>69400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>86300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>49300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>72800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>46900</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>4831400</v>
+      </c>
+      <c r="E46" s="3">
         <v>4774200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4599200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4601000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4737500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4280700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3598200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3869000</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>286200</v>
+      </c>
+      <c r="E47" s="3">
         <v>256400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>191300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>379700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>289200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>255800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>239800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>215200</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>2878700</v>
+      </c>
+      <c r="E48" s="3">
         <v>2749300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2789900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2749300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2709600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2457300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1822800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1687300</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>3641100</v>
+      </c>
+      <c r="E49" s="3">
         <v>3451800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3612000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4239300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4266200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4289000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4231400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4168000</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1737,9 +1853,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1764,21 +1883,24 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>364900</v>
+      </c>
+      <c r="E52" s="3">
         <v>307200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>269800</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
       <c r="G52" s="3">
         <v>0</v>
       </c>
@@ -1791,9 +1913,12 @@
       <c r="J52" s="3">
         <v>0</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1818,36 +1943,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>12209800</v>
+      </c>
+      <c r="E54" s="3">
         <v>12108000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12052800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12135800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12217000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11536500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10114500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10159400</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1859,8 +1990,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -1872,170 +2004,189 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>607900</v>
+      </c>
+      <c r="E57" s="3">
         <v>326000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>417900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>671500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>755200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>818200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>735300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>635700</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>152500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1085700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>135600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>56500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>437400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>520500</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>446600</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>848800</v>
+      </c>
+      <c r="E59" s="3">
         <v>577500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>600000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>407900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>427100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>348200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>310300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>385000</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>1609100</v>
+      </c>
+      <c r="E60" s="3">
         <v>2506700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1639900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1463500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1911100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1968800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1289700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1685500</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1283800</v>
+      </c>
+      <c r="E61" s="3">
         <v>689700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1870400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2076400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2212500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2063200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2031700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2719000</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>96400</v>
+      </c>
+      <c r="E62" s="3">
         <v>17700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>24700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>106700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>143400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>128300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>158000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>250200</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2060,9 +2211,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2087,9 +2241,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2114,36 +2271,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>3070900</v>
+      </c>
+      <c r="E66" s="3">
         <v>3334200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3694800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3799400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4471400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4521000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3814400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4976700</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2155,8 +2318,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2181,9 +2345,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2208,9 +2375,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2235,9 +2405,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2262,36 +2435,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>6785800</v>
+      </c>
+      <c r="E72" s="3">
         <v>6311700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6576700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6974800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7008000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6559000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5831800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5545200</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2316,9 +2495,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2343,9 +2525,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2370,36 +2555,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>9138900</v>
+      </c>
+      <c r="E76" s="3">
         <v>8773900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8358000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8336300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7745700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7014900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6299400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5181600</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2424,68 +2615,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44286</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43921</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43555</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>781200</v>
+      </c>
+      <c r="E81" s="3">
         <v>703300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>671900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>731400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>698600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>791900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>717200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>859600</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2497,35 +2697,39 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>426800</v>
+      </c>
+      <c r="E83" s="3">
         <v>292200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>307400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>484900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>487600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>486600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>397400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>395800</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2550,9 +2754,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2577,9 +2784,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2604,9 +2814,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2631,9 +2844,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2658,36 +2874,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>1407700</v>
+      </c>
+      <c r="E89" s="3">
         <v>967400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>884200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1165000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1098400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1091800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>844400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1078700</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2699,35 +2921,39 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-458200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-401500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-396400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-440700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-563500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-579100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-354900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300000</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2752,9 +2978,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -2779,36 +3008,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-550800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-538600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-444700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-646100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-771400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-787300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-675000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-415300</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -2820,20 +3055,21 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>237900</v>
+      </c>
+      <c r="E96" s="3">
         <v>211600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>209900</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
@@ -2846,9 +3082,12 @@
       <c r="J96" s="3">
         <v>0</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -2873,9 +3112,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -2900,9 +3142,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -2927,88 +3172,100 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-726300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-410400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-651100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-583700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-67200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>130200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-609500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-38900</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="E101" s="3">
         <v>97700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>76800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>101700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>46500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-26600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>35300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-33300</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>113500</v>
+      </c>
+      <c r="E102" s="3">
         <v>116100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-134900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>36900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>306300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>408100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-404700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>591200</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/TRUMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TRUMY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
   <si>
     <t>TRUMY</t>
   </si>
@@ -295,9 +295,6 @@
   </si>
   <si>
     <t xml:space="preserve">Change In Cash and Cash Equivalents </t>
-  </si>
-  <si>
-    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -814,8 +811,8 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>91</v>
+      <c r="D12" s="3">
+        <v>635300</v>
       </c>
       <c r="E12" s="3">
         <v>552800</v>
@@ -875,7 +872,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>124600</v>
+        <v>168400</v>
       </c>
       <c r="E14" s="3">
         <v>3900</v>
@@ -905,7 +902,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>570600</v>
+        <v>414900</v>
       </c>
       <c r="E15" s="3">
         <v>377700</v>
@@ -946,7 +943,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>5741900</v>
+        <v>5697900</v>
       </c>
       <c r="E17" s="3">
         <v>5165500</v>
@@ -976,7 +973,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1177500</v>
+        <v>1221500</v>
       </c>
       <c r="E18" s="3">
         <v>929300</v>
@@ -1020,7 +1017,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>3200</v>
+        <v>30700</v>
       </c>
       <c r="E20" s="3">
         <v>-2700</v>
@@ -1050,7 +1047,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>1745000</v>
+        <v>1605700</v>
       </c>
       <c r="E21" s="3">
         <v>1309700</v>
@@ -1080,7 +1077,7 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>41700</v>
+        <v>13500</v>
       </c>
       <c r="E22" s="3">
         <v>13700</v>
@@ -1380,7 +1377,7 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-3200</v>
+        <v>-30700</v>
       </c>
       <c r="E32" s="3">
         <v>2700</v>
@@ -1593,7 +1590,7 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="E42" s="3">
         <v>9700</v>
@@ -1683,7 +1680,7 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>181400</v>
+        <v>83400</v>
       </c>
       <c r="E45" s="3">
         <v>238900</v>
@@ -1803,7 +1800,7 @@
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>3641100</v>
+        <v>3255700</v>
       </c>
       <c r="E49" s="3">
         <v>3451800</v>
@@ -2011,7 +2008,7 @@
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>607900</v>
+        <v>349900</v>
       </c>
       <c r="E57" s="3">
         <v>326000</v>
@@ -2041,7 +2038,7 @@
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>152500</v>
+        <v>150600</v>
       </c>
       <c r="E58" s="3">
         <v>1085700</v>
@@ -2071,7 +2068,7 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>848800</v>
+        <v>535300</v>
       </c>
       <c r="E59" s="3">
         <v>577500</v>
@@ -2131,7 +2128,7 @@
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>1283800</v>
+        <v>1278200</v>
       </c>
       <c r="E61" s="3">
         <v>689700</v>
@@ -2161,7 +2158,7 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>96400</v>
+        <v>37900</v>
       </c>
       <c r="E62" s="3">
         <v>17700</v>
@@ -2704,7 +2701,7 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>426800</v>
+        <v>326600</v>
       </c>
       <c r="E83" s="3">
         <v>292200</v>
